--- a/resource/groundTruths/architecture/CF_M01_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M01_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D81AD28-2E1C-234D-9248-A5FE70687B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C52754-3E21-9847-953C-BD3AD983549A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17040" xr2:uid="{CA8FAF20-B9F3-514A-BF31-60DAC8067722}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16960" xr2:uid="{CA8FAF20-B9F3-514A-BF31-60DAC8067722}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="151">
   <si>
     <t>Document ID</t>
   </si>
@@ -86,9 +86,6 @@
     <t>The client is the user of the platform</t>
   </si>
   <si>
-    <t>CF_M01_AD01</t>
-  </si>
-  <si>
     <t>CF_M01_AU02</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
   </si>
   <si>
-    <t>CF_M01_AD02</t>
-  </si>
-  <si>
     <t>CF_M01_AU06</t>
   </si>
   <si>
@@ -308,18 +302,12 @@
     <t>CF_M01_AU16</t>
   </si>
   <si>
-    <t>AWS cloud services suite</t>
-  </si>
-  <si>
     <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
   </si>
   <si>
     <t>44, 45</t>
   </si>
   <si>
-    <t>The services used have different main functions that together allow the creation of the necessary infrastructure to manage the data on the platform. The main functions are the following: storage, data reading and data transmission.</t>
-  </si>
-  <si>
     <t>CF_M01_AU17</t>
   </si>
   <si>
@@ -377,21 +365,12 @@
     <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
   </si>
   <si>
-    <t>AD ID</t>
-  </si>
-  <si>
     <t>Architectural Pattern</t>
   </si>
   <si>
-    <t>CF_M01_AD03</t>
-  </si>
-  <si>
     <t>CF_M01_AU06, CF_M01_AU07</t>
   </si>
   <si>
-    <t>CF_M01_AD04</t>
-  </si>
-  <si>
     <t>Design Pattern</t>
   </si>
   <si>
@@ -417,13 +396,106 @@
   </si>
   <si>
     <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+  </si>
+  <si>
+    <t>P ID</t>
+  </si>
+  <si>
+    <t>CF_M01_P01</t>
+  </si>
+  <si>
+    <t>CF_M01_P02</t>
+  </si>
+  <si>
+    <t>CF_M01_P03</t>
+  </si>
+  <si>
+    <t>CF_M01_P04</t>
+  </si>
+  <si>
+    <t>AWS cloud services set</t>
+  </si>
+  <si>
+    <t>The Web Platform communicates with the API Gateway.</t>
+  </si>
+  <si>
+    <t>The Mobile Platform communicates with the API Gateway.</t>
+  </si>
+  <si>
+    <t>The Web Socket service communicates with the Cloud Services.</t>
+  </si>
+  <si>
+    <t>The Web Socket service communicates with the Database.</t>
+  </si>
+  <si>
+    <t>The Core service communicates with the Database.</t>
+  </si>
+  <si>
+    <t>The Core service communicates with the Cloud Services.</t>
+  </si>
+  <si>
+    <t>The Analytical Module communicates with the Cloud Services.</t>
+  </si>
+  <si>
+    <t>The Analytical Module communicates with the Database.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU10, CF_M01_AU08</t>
+  </si>
+  <si>
+    <t>CF_M01_AU10, CF_M01_AU09</t>
+  </si>
+  <si>
+    <t>CF_M01_AU14, CF_M01_AU15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CF_M01_AU14, CF_M01_AU16</t>
+  </si>
+  <si>
+    <t>CF_M01_AU11, CF_M01_AU15</t>
+  </si>
+  <si>
+    <t>CF_M01_AU11, CF_M01_AU16</t>
+  </si>
+  <si>
+    <t>CF_M01_AU12, CF_M01_AU16</t>
+  </si>
+  <si>
+    <t>CF_M01_AU35</t>
+  </si>
+  <si>
+    <t>CF_M01_AU36</t>
+  </si>
+  <si>
+    <t>CF_M01_AU37</t>
+  </si>
+  <si>
+    <t>CF_M01_AU38</t>
+  </si>
+  <si>
+    <t>CF_M01_AU39</t>
+  </si>
+  <si>
+    <t>CF_M01_AU40</t>
+  </si>
+  <si>
+    <t>CF_M01_AU41</t>
+  </si>
+  <si>
+    <t>CF_M01_AU42</t>
+  </si>
+  <si>
+    <t>CF_M01_AU43</t>
+  </si>
+  <si>
+    <t>MySQL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -448,6 +520,12 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -514,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -562,6 +640,7 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -907,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2ADE25-2A22-5748-962B-820C819CA041}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.5" customWidth="1"/>
@@ -974,7 +1053,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="G3" s="9">
         <v>41</v>
@@ -985,19 +1064,19 @@
         <v>7</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>19</v>
-      </c>
       <c r="F4" s="11" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="G4" s="13">
         <v>41</v>
@@ -1008,19 +1087,19 @@
         <v>7</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="E5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>24</v>
       </c>
       <c r="G5" s="17">
         <v>41</v>
@@ -1031,19 +1110,19 @@
         <v>7</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>27</v>
-      </c>
       <c r="E6" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="13">
         <v>41</v>
@@ -1054,19 +1133,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="E7" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="9">
         <v>41</v>
@@ -1077,19 +1156,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>33</v>
-      </c>
       <c r="F8" s="11" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="G8" s="13">
         <v>41</v>
@@ -1100,19 +1179,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>37</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="G9" s="9">
         <v>41</v>
@@ -1123,19 +1202,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>40</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="G10" s="13">
         <v>41</v>
@@ -1146,19 +1225,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="E11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" s="9">
         <v>42</v>
@@ -1169,19 +1248,19 @@
         <v>7</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>44</v>
-      </c>
       <c r="F12" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" s="13">
         <v>42</v>
@@ -1192,17 +1271,17 @@
         <v>7</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G13" s="17">
         <v>42</v>
@@ -1213,17 +1292,17 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G14" s="5">
         <v>42</v>
@@ -1234,17 +1313,17 @@
         <v>7</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G15" s="17">
         <v>42</v>
@@ -1255,17 +1334,17 @@
         <v>7</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G16" s="5">
         <v>43</v>
@@ -1276,17 +1355,17 @@
         <v>7</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G17" s="17">
         <v>43</v>
@@ -1297,17 +1376,17 @@
         <v>7</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G18" s="5">
         <v>44</v>
@@ -1318,17 +1397,17 @@
         <v>7</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G19" s="17">
         <v>44</v>
@@ -1339,19 +1418,19 @@
         <v>7</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="F20" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G20" s="5">
         <v>44</v>
@@ -1362,19 +1441,19 @@
         <v>7</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="F21" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G21" s="17">
         <v>44</v>
@@ -1385,19 +1464,19 @@
         <v>7</v>
       </c>
       <c r="B22" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>72</v>
-      </c>
       <c r="F22" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G22" s="5">
         <v>44</v>
@@ -1408,19 +1487,19 @@
         <v>7</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="F23" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G23" s="17">
         <v>44</v>
@@ -1431,19 +1510,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>78</v>
-      </c>
       <c r="F24" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G24" s="5">
         <v>44</v>
@@ -1454,17 +1533,17 @@
         <v>7</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="16"/>
       <c r="E25" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G25" s="17">
         <v>44</v>
@@ -1475,17 +1554,17 @@
         <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G26" s="5">
         <v>44</v>
@@ -1496,19 +1575,19 @@
         <v>7</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="F27" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" s="9">
         <v>44</v>
@@ -1519,188 +1598,348 @@
         <v>7</v>
       </c>
       <c r="B28" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="12" t="s">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="C29" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="13" t="s">
+      <c r="E29" s="12" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="8" t="s">
+      <c r="F29" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" s="9">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="11" t="s">
+      <c r="C30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="E30" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="F30" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="13">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="7" t="s">
+      <c r="C31" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="8" t="s">
+      <c r="E31" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="F31" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="13">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F31" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="9">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="11" t="s">
+      <c r="C32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="E32" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="F32" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F32" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="G32" s="13">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="7" t="s">
+      <c r="C33" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="8" t="s">
+      <c r="E33" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="F33" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="F33" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="G33" s="9">
-        <v>49</v>
-      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="11" t="s">
+      <c r="A34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" s="12" t="s">
+      <c r="C34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F34" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>109</v>
+      <c r="F34" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G34" s="9">
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="G35" s="9">
-        <v>51</v>
+      <c r="B35" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>126</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>127</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G37">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G38">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G39">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
+        <v>131</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="G40">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="G42">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" t="s">
+        <v>150</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G43">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C35" xr:uid="{18AE1B65-65D6-C74C-AF0C-0BCA4FC93AAE}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C42" xr:uid="{18AE1B65-65D6-C74C-AF0C-0BCA4FC93AAE}">
       <formula1>"Layer,Component,Service,Other,Technology"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1718,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1741,16 +1980,16 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="C2" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>114</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>121</v>
       </c>
       <c r="F2" s="21"/>
       <c r="G2" s="21">
@@ -1762,19 +2001,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="G3" s="22">
         <v>41</v>
@@ -1785,19 +2024,19 @@
         <v>7</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G4" s="21">
         <v>42</v>
@@ -1808,19 +2047,19 @@
         <v>7</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D5" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="24" t="s">
-        <v>126</v>
-      </c>
       <c r="F5" s="22" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G5" s="22">
         <v>43</v>

--- a/resource/groundTruths/architecture/CF_M01_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M01_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C52754-3E21-9847-953C-BD3AD983549A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF35C87-C6C2-6E42-BCFB-DC681FE28CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16960" xr2:uid="{CA8FAF20-B9F3-514A-BF31-60DAC8067722}"/>
+    <workbookView xWindow="1300" yWindow="760" windowWidth="29400" windowHeight="16880" xr2:uid="{CA8FAF20-B9F3-514A-BF31-60DAC8067722}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="135">
   <si>
     <t>Document ID</t>
   </si>
@@ -191,311 +191,263 @@
     <t>CF_M01_AU05, CF_M01_AU10</t>
   </si>
   <si>
+    <t>CF_M01_AU26</t>
+  </si>
+  <si>
+    <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+  </si>
+  <si>
+    <t>CF_M01_AU27</t>
+  </si>
+  <si>
+    <t>CF_M01_AU28</t>
+  </si>
+  <si>
+    <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+  </si>
+  <si>
+    <t>CF_M01_AU29</t>
+  </si>
+  <si>
+    <t>CF_M01_AU10</t>
+  </si>
+  <si>
+    <t>API Gateway Service</t>
+  </si>
+  <si>
+    <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU11</t>
+  </si>
+  <si>
+    <t>Core Service</t>
+  </si>
+  <si>
+    <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU12</t>
+  </si>
+  <si>
+    <t>Analytical module</t>
+  </si>
+  <si>
+    <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU13</t>
+  </si>
+  <si>
+    <t>Api Player</t>
+  </si>
+  <si>
+    <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
+  </si>
+  <si>
+    <t>CF_M01_AU14</t>
+  </si>
+  <si>
+    <t>Web Socket</t>
+  </si>
+  <si>
+    <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU31</t>
+  </si>
+  <si>
+    <t>This service is responsible for communicating with players.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU32</t>
+  </si>
+  <si>
+    <t>This service is responsible for communicating between the platform and the players.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU15</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>SQL database</t>
+  </si>
+  <si>
+    <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU16</t>
+  </si>
+  <si>
+    <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+  </si>
+  <si>
+    <t>44, 45</t>
+  </si>
+  <si>
+    <t>CF_M01_AU17</t>
+  </si>
+  <si>
+    <t>Amazon S3</t>
+  </si>
+  <si>
+    <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU18</t>
+  </si>
+  <si>
+    <t>Amazon DynamoDB</t>
+  </si>
+  <si>
+    <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU20</t>
+  </si>
+  <si>
+    <t>Amazon Athena</t>
+  </si>
+  <si>
+    <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
+  </si>
+  <si>
+    <t>CF_M01_AU21</t>
+  </si>
+  <si>
+    <t>AWS Glue</t>
+  </si>
+  <si>
+    <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
+  </si>
+  <si>
+    <t>CF_M01_AU22</t>
+  </si>
+  <si>
+    <t>Kinesis Data Streams</t>
+  </si>
+  <si>
+    <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+  </si>
+  <si>
+    <t>50, 51</t>
+  </si>
+  <si>
+    <t>CF_M01_AU23</t>
+  </si>
+  <si>
+    <t>Kinesis Data Firehose</t>
+  </si>
+  <si>
+    <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+  </si>
+  <si>
+    <t>Architectural Pattern</t>
+  </si>
+  <si>
+    <t>CF_M01_AU06, CF_M01_AU07</t>
+  </si>
+  <si>
+    <t>Design Pattern</t>
+  </si>
+  <si>
+    <t>API Gateway</t>
+  </si>
+  <si>
+    <t>Client-Server</t>
+  </si>
+  <si>
+    <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+  </si>
+  <si>
+    <t>Three Layers</t>
+  </si>
+  <si>
+    <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
+  </si>
+  <si>
+    <t>Service-oriented</t>
+  </si>
+  <si>
+    <t>Both the business layer and the data layer are divided into several different services</t>
+  </si>
+  <si>
+    <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+  </si>
+  <si>
+    <t>P ID</t>
+  </si>
+  <si>
+    <t>CF_M01_P01</t>
+  </si>
+  <si>
+    <t>CF_M01_P02</t>
+  </si>
+  <si>
+    <t>CF_M01_P03</t>
+  </si>
+  <si>
+    <t>CF_M01_P04</t>
+  </si>
+  <si>
+    <t>AWS cloud services set</t>
+  </si>
+  <si>
+    <t>MySQL</t>
+  </si>
+  <si>
+    <t>CF_M01_AU24, CF_M01_AU25</t>
+  </si>
+  <si>
+    <t>CF_M01_AU26,CF_M01_AU27</t>
+  </si>
+  <si>
+    <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
+  </si>
+  <si>
+    <t>CF_M01_AU27, CF_M01_AU13</t>
+  </si>
+  <si>
+    <t>CF_M01_AU27, CF_M01_AU14</t>
+  </si>
+  <si>
+    <t>TCP</t>
+  </si>
+  <si>
+    <t>AWSS RDS</t>
+  </si>
+  <si>
+    <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+  </si>
+  <si>
+    <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+  </si>
+  <si>
+    <t>NestJS</t>
+  </si>
+  <si>
+    <t>TypeScript</t>
+  </si>
+  <si>
     <t>CF_M01_AU34</t>
   </si>
   <si>
-    <t>via the HTTP protocol</t>
-  </si>
-  <si>
-    <t>CF_M01_AU25, CF_M01_AU33</t>
-  </si>
-  <si>
-    <t>CF_M01_AU26</t>
-  </si>
-  <si>
-    <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
-  </si>
-  <si>
-    <t>CF_M01_AU10, CF_M01_AU11</t>
-  </si>
-  <si>
-    <t>CF_M01_AU27</t>
-  </si>
-  <si>
-    <t>CF_M01_AU10, CF_M01_AU12</t>
-  </si>
-  <si>
-    <t>CF_M01_AU28</t>
-  </si>
-  <si>
-    <t>communication between the Api Gateway service is via the TCP communication protocol</t>
-  </si>
-  <si>
-    <t>CF_M01_AU29</t>
-  </si>
-  <si>
-    <t>CF_M01_AU10</t>
-  </si>
-  <si>
-    <t>API Gateway Service</t>
-  </si>
-  <si>
-    <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU11</t>
-  </si>
-  <si>
-    <t>Core Service</t>
-  </si>
-  <si>
-    <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU12</t>
-  </si>
-  <si>
-    <t>Analytical module</t>
-  </si>
-  <si>
-    <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU13</t>
-  </si>
-  <si>
-    <t>Api Player</t>
-  </si>
-  <si>
-    <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
-  </si>
-  <si>
-    <t>CF_M01_AU14</t>
-  </si>
-  <si>
-    <t>Web Socket</t>
-  </si>
-  <si>
-    <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU31</t>
-  </si>
-  <si>
-    <t>This service is responsible for communicating with players.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU30, CF_M01_AU13</t>
-  </si>
-  <si>
-    <t>CF_M01_AU32</t>
-  </si>
-  <si>
-    <t>This service is responsible for communicating between the platform and the players.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU30, CF_M01_AU14</t>
-  </si>
-  <si>
-    <t>CF_M01_AU15</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>SQL database</t>
-  </si>
-  <si>
-    <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU16</t>
-  </si>
-  <si>
-    <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-  </si>
-  <si>
-    <t>44, 45</t>
-  </si>
-  <si>
-    <t>CF_M01_AU17</t>
-  </si>
-  <si>
-    <t>Amazon S3</t>
-  </si>
-  <si>
-    <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU18</t>
-  </si>
-  <si>
-    <t>Amazon DynamoDB</t>
-  </si>
-  <si>
-    <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU20</t>
-  </si>
-  <si>
-    <t>Amazon Athena</t>
-  </si>
-  <si>
-    <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
-  </si>
-  <si>
-    <t>CF_M01_AU21</t>
-  </si>
-  <si>
-    <t>AWS Glue</t>
-  </si>
-  <si>
-    <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
-  </si>
-  <si>
-    <t>CF_M01_AU22</t>
-  </si>
-  <si>
-    <t>Kinesis Data Streams</t>
-  </si>
-  <si>
-    <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
-  </si>
-  <si>
-    <t>50, 51</t>
-  </si>
-  <si>
-    <t>CF_M01_AU23</t>
-  </si>
-  <si>
-    <t>Kinesis Data Firehose</t>
-  </si>
-  <si>
-    <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
-  </si>
-  <si>
-    <t>Architectural Pattern</t>
-  </si>
-  <si>
-    <t>CF_M01_AU06, CF_M01_AU07</t>
-  </si>
-  <si>
-    <t>Design Pattern</t>
-  </si>
-  <si>
-    <t>API Gateway</t>
-  </si>
-  <si>
-    <t>Client-Server</t>
-  </si>
-  <si>
-    <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
-  </si>
-  <si>
-    <t>Three Layers</t>
-  </si>
-  <si>
-    <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
-  </si>
-  <si>
-    <t>Service-oriented</t>
-  </si>
-  <si>
-    <t>Both the business layer and the data layer are divided into several different services</t>
-  </si>
-  <si>
-    <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
-  </si>
-  <si>
-    <t>P ID</t>
-  </si>
-  <si>
-    <t>CF_M01_P01</t>
-  </si>
-  <si>
-    <t>CF_M01_P02</t>
-  </si>
-  <si>
-    <t>CF_M01_P03</t>
-  </si>
-  <si>
-    <t>CF_M01_P04</t>
-  </si>
-  <si>
-    <t>AWS cloud services set</t>
-  </si>
-  <si>
-    <t>The Web Platform communicates with the API Gateway.</t>
-  </si>
-  <si>
-    <t>The Mobile Platform communicates with the API Gateway.</t>
-  </si>
-  <si>
-    <t>The Web Socket service communicates with the Cloud Services.</t>
-  </si>
-  <si>
-    <t>The Web Socket service communicates with the Database.</t>
-  </si>
-  <si>
-    <t>The Core service communicates with the Database.</t>
-  </si>
-  <si>
-    <t>The Core service communicates with the Cloud Services.</t>
-  </si>
-  <si>
-    <t>The Analytical Module communicates with the Cloud Services.</t>
-  </si>
-  <si>
-    <t>The Analytical Module communicates with the Database.</t>
-  </si>
-  <si>
-    <t>CF_M01_AU10, CF_M01_AU08</t>
-  </si>
-  <si>
-    <t>CF_M01_AU10, CF_M01_AU09</t>
-  </si>
-  <si>
-    <t>CF_M01_AU14, CF_M01_AU15</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CF_M01_AU14, CF_M01_AU16</t>
-  </si>
-  <si>
-    <t>CF_M01_AU11, CF_M01_AU15</t>
-  </si>
-  <si>
-    <t>CF_M01_AU11, CF_M01_AU16</t>
-  </si>
-  <si>
-    <t>CF_M01_AU12, CF_M01_AU16</t>
-  </si>
-  <si>
     <t>CF_M01_AU35</t>
   </si>
   <si>
-    <t>CF_M01_AU36</t>
-  </si>
-  <si>
-    <t>CF_M01_AU37</t>
-  </si>
-  <si>
-    <t>CF_M01_AU38</t>
-  </si>
-  <si>
-    <t>CF_M01_AU39</t>
-  </si>
-  <si>
-    <t>CF_M01_AU40</t>
-  </si>
-  <si>
-    <t>CF_M01_AU41</t>
-  </si>
-  <si>
-    <t>CF_M01_AU42</t>
-  </si>
-  <si>
-    <t>CF_M01_AU43</t>
-  </si>
-  <si>
-    <t>MySQL</t>
+    <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
+  </si>
+  <si>
+    <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -520,12 +472,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -640,7 +586,9 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -986,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2ADE25-2A22-5748-962B-820C819CA041}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.5" customWidth="1"/>
@@ -1020,7 +968,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1053,7 +1001,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G3" s="9">
         <v>41</v>
@@ -1076,7 +1024,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G4" s="13">
         <v>41</v>
@@ -1122,7 +1070,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="G6" s="13">
         <v>41</v>
@@ -1168,7 +1116,7 @@
         <v>32</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G8" s="13">
         <v>41</v>
@@ -1191,7 +1139,7 @@
         <v>35</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G9" s="9">
         <v>41</v>
@@ -1214,7 +1162,7 @@
         <v>38</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G10" s="13">
         <v>41</v>
@@ -1271,7 +1219,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>20</v>
@@ -1309,24 +1257,24 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="15" t="s">
+      <c r="A15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16" t="s">
+      <c r="C15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="17">
-        <v>42</v>
+      <c r="F15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="5">
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1334,240 +1282,248 @@
         <v>7</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="E16" s="4" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="17">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="17">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" s="17">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="5">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="15" t="s">
+      <c r="C23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="17">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="9">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="17">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="17">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="17">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="17">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="5">
-        <v>44</v>
+      <c r="G26" s="13">
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1575,22 +1531,22 @@
         <v>7</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>36</v>
+        <v>88</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>80</v>
       </c>
       <c r="G27" s="9">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1598,160 +1554,160 @@
         <v>7</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="13">
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="11" t="s">
+      <c r="A29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="13">
-        <v>45</v>
+      <c r="D29" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="9">
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="7" t="s">
+      <c r="A30" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="9">
-        <v>45</v>
+      <c r="D30" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="11" t="s">
+      <c r="A31" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="13">
-        <v>49</v>
+      <c r="D31" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" s="9">
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" s="7" t="s">
+      <c r="B32" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>100</v>
+      <c r="D32" t="s">
+        <v>119</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="9">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="7" t="s">
+      <c r="B34" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="G34" s="9">
-        <v>51</v>
+      <c r="D34" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34">
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -1759,187 +1715,27 @@
         <v>7</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
         <v>126</v>
       </c>
-      <c r="F35" s="11" t="s">
-        <v>134</v>
+      <c r="E35" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="G35">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" t="s">
-        <v>127</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="G36">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" t="s">
-        <v>128</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" t="s">
-        <v>129</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="G38">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" t="s">
-        <v>130</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G39">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" t="s">
-        <v>131</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="G40">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" t="s">
-        <v>132</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G41">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" t="s">
-        <v>133</v>
-      </c>
-      <c r="F42" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="G42">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" t="s">
-        <v>150</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="G43">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C42" xr:uid="{18AE1B65-65D6-C74C-AF0C-0BCA4FC93AAE}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C31" xr:uid="{18AE1B65-65D6-C74C-AF0C-0BCA4FC93AAE}">
       <formula1>"Layer,Component,Service,Other,Technology"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1957,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1980,16 +1776,16 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F2" s="21"/>
       <c r="G2" s="21">
@@ -2001,19 +1797,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>116</v>
-      </c>
       <c r="F3" s="22" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G3" s="22">
         <v>41</v>
@@ -2024,19 +1820,19 @@
         <v>7</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G4" s="21">
         <v>42</v>
@@ -2047,19 +1843,19 @@
         <v>7</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D5" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="24" t="s">
-        <v>119</v>
-      </c>
       <c r="F5" s="22" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G5" s="22">
         <v>43</v>

--- a/resource/groundTruths/architecture/CF_M01_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M01_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF35C87-C6C2-6E42-BCFB-DC681FE28CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FD4153-C0D4-7340-8B9B-C71D8BA273D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1300" yWindow="760" windowWidth="29400" windowHeight="16880" xr2:uid="{CA8FAF20-B9F3-514A-BF31-60DAC8067722}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{CA8FAF20-B9F3-514A-BF31-60DAC8067722}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -80,9 +80,6 @@
     <t>Other</t>
   </si>
   <si>
-    <t>Customer</t>
-  </si>
-  <si>
     <t>The client is the user of the platform</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
     <t>CF_M01_AU25</t>
   </si>
   <si>
-    <t>more specifically with the Api Gateway</t>
-  </si>
-  <si>
     <t>CF_M01_AU05, CF_M01_AU10</t>
   </si>
   <si>
@@ -441,6 +435,12 @@
   </si>
   <si>
     <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
+  </si>
+  <si>
+    <t>the presentation layer communicates with the business layer more specifically with the Api Gateway</t>
+  </si>
+  <si>
+    <t>Client</t>
   </si>
 </sst>
 </file>
@@ -968,7 +968,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -995,13 +995,13 @@
         <v>13</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>15</v>
-      </c>
       <c r="F3" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G3" s="9">
         <v>41</v>
@@ -1012,19 +1012,19 @@
         <v>7</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>18</v>
-      </c>
       <c r="F4" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G4" s="13">
         <v>41</v>
@@ -1035,19 +1035,19 @@
         <v>7</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="E5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>23</v>
       </c>
       <c r="G5" s="17">
         <v>41</v>
@@ -1058,19 +1058,19 @@
         <v>7</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>26</v>
-      </c>
       <c r="E6" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G6" s="13">
         <v>41</v>
@@ -1081,19 +1081,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="E7" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="9">
         <v>41</v>
@@ -1104,19 +1104,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>32</v>
-      </c>
       <c r="F8" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G8" s="13">
         <v>41</v>
@@ -1127,19 +1127,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G9" s="9">
         <v>41</v>
@@ -1150,19 +1150,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>38</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G10" s="13">
         <v>41</v>
@@ -1173,19 +1173,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="D11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" s="9">
         <v>42</v>
@@ -1196,19 +1196,19 @@
         <v>7</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>44</v>
-      </c>
       <c r="E12" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" s="13">
         <v>42</v>
@@ -1222,14 +1222,14 @@
         <v>8</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>46</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>47</v>
       </c>
       <c r="G13" s="17">
         <v>42</v>
@@ -1240,17 +1240,17 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G14" s="5">
         <v>42</v>
@@ -1261,17 +1261,17 @@
         <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G15" s="5">
         <v>43</v>
@@ -1282,19 +1282,19 @@
         <v>7</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G16" s="5">
         <v>44</v>
@@ -1305,19 +1305,19 @@
         <v>7</v>
       </c>
       <c r="B17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>59</v>
-      </c>
       <c r="F17" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17" s="5">
         <v>44</v>
@@ -1328,19 +1328,19 @@
         <v>7</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="F18" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" s="17">
         <v>44</v>
@@ -1351,19 +1351,19 @@
         <v>7</v>
       </c>
       <c r="B19" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>65</v>
-      </c>
       <c r="F19" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" s="5">
         <v>44</v>
@@ -1374,19 +1374,19 @@
         <v>7</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="F20" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" s="17">
         <v>44</v>
@@ -1397,19 +1397,19 @@
         <v>7</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>71</v>
-      </c>
       <c r="F21" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G21" s="5">
         <v>44</v>
@@ -1420,17 +1420,17 @@
         <v>7</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G22" s="17">
         <v>44</v>
@@ -1441,17 +1441,17 @@
         <v>7</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G23" s="5">
         <v>44</v>
@@ -1462,19 +1462,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="E24" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="F24" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G24" s="9">
         <v>44</v>
@@ -1485,22 +1485,22 @@
         <v>7</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1508,19 +1508,19 @@
         <v>7</v>
       </c>
       <c r="B26" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="F26" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G26" s="13">
         <v>45</v>
@@ -1531,19 +1531,19 @@
         <v>7</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="F27" s="20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G27" s="9">
         <v>45</v>
@@ -1554,19 +1554,19 @@
         <v>7</v>
       </c>
       <c r="B28" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>91</v>
-      </c>
       <c r="F28" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G28" s="13">
         <v>49</v>
@@ -1577,19 +1577,19 @@
         <v>7</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="F29" s="20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G29" s="9">
         <v>49</v>
@@ -1600,22 +1600,22 @@
         <v>7</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="F30" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1623,19 +1623,19 @@
         <v>7</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>101</v>
-      </c>
       <c r="F31" s="20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G31" s="9">
         <v>51</v>
@@ -1646,19 +1646,19 @@
         <v>7</v>
       </c>
       <c r="B32" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>76</v>
       </c>
       <c r="G32">
         <v>44</v>
@@ -1669,19 +1669,19 @@
         <v>7</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G33">
         <v>44</v>
@@ -1692,19 +1692,19 @@
         <v>7</v>
       </c>
       <c r="B34" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" t="s">
-        <v>130</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>133</v>
-      </c>
       <c r="F34" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G34">
         <v>44</v>
@@ -1715,19 +1715,19 @@
         <v>7</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="F35" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G35">
         <v>44</v>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1776,16 +1776,16 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F2" s="21"/>
       <c r="G2" s="21">
@@ -1797,19 +1797,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G3" s="22">
         <v>41</v>
@@ -1820,19 +1820,19 @@
         <v>7</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G4" s="21">
         <v>42</v>
@@ -1843,19 +1843,19 @@
         <v>7</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G5" s="22">
         <v>43</v>

--- a/resource/groundTruths/architecture/CF_M01_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M01_ground_truth_architecture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FD4153-C0D4-7340-8B9B-C71D8BA273D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D577233-7E1C-7E4B-A3EF-B231788E0608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{CA8FAF20-B9F3-514A-BF31-60DAC8067722}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="135">
   <si>
     <t>Document ID</t>
   </si>
@@ -98,9 +98,6 @@
     <t>Connector</t>
   </si>
   <si>
-    <t>Internet</t>
-  </si>
-  <si>
     <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
   </si>
   <si>
@@ -441,6 +438,9 @@
   </si>
   <si>
     <t>Client</t>
+  </si>
+  <si>
+    <t>Fixed Type</t>
   </si>
 </sst>
 </file>
@@ -934,13 +934,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2ADE25-2A22-5748-962B-820C819CA041}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -962,13 +962,16 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -984,7 +987,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
@@ -995,19 +998,19 @@
         <v>13</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G3" s="9">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
@@ -1024,13 +1027,13 @@
         <v>17</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G4" s="13">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
@@ -1040,57 +1043,55 @@
       <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>22</v>
       </c>
       <c r="G5" s="17">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G6" s="13">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="E7" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>18</v>
@@ -1099,122 +1100,122 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>31</v>
-      </c>
       <c r="F8" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G8" s="13">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G9" s="9">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>37</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G10" s="13">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="D11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="9">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="E12" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="13">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>7</v>
       </c>
@@ -1226,75 +1227,75 @@
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>46</v>
       </c>
       <c r="G13" s="17">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14" s="5">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G15" s="5">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G16" s="5">
         <v>44</v>
@@ -1305,19 +1306,19 @@
         <v>7</v>
       </c>
       <c r="B17" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="E17" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>57</v>
-      </c>
       <c r="F17" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" s="5">
         <v>44</v>
@@ -1328,19 +1329,19 @@
         <v>7</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="F18" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" s="17">
         <v>44</v>
@@ -1351,19 +1352,19 @@
         <v>7</v>
       </c>
       <c r="B19" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="12" t="s">
+      <c r="E19" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>63</v>
-      </c>
       <c r="F19" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" s="5">
         <v>44</v>
@@ -1374,19 +1375,19 @@
         <v>7</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>66</v>
-      </c>
       <c r="F20" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" s="17">
         <v>44</v>
@@ -1397,19 +1398,19 @@
         <v>7</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="12" t="s">
+      <c r="E21" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="12" t="s">
-        <v>69</v>
-      </c>
       <c r="F21" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="5">
         <v>44</v>
@@ -1420,17 +1421,17 @@
         <v>7</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G22" s="17">
         <v>44</v>
@@ -1441,17 +1442,17 @@
         <v>7</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G23" s="5">
         <v>44</v>
@@ -1462,19 +1463,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="D24" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="E24" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="F24" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G24" s="9">
         <v>44</v>
@@ -1485,22 +1486,22 @@
         <v>7</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" s="12" t="s">
+      <c r="F25" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>79</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1508,19 +1509,19 @@
         <v>7</v>
       </c>
       <c r="B26" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="12" t="s">
+      <c r="E26" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E26" s="12" t="s">
-        <v>83</v>
-      </c>
       <c r="F26" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G26" s="13">
         <v>45</v>
@@ -1531,19 +1532,19 @@
         <v>7</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="E27" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>86</v>
-      </c>
       <c r="F27" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G27" s="9">
         <v>45</v>
@@ -1554,19 +1555,19 @@
         <v>7</v>
       </c>
       <c r="B28" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="12" t="s">
+      <c r="E28" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>89</v>
-      </c>
       <c r="F28" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G28" s="13">
         <v>49</v>
@@ -1577,19 +1578,19 @@
         <v>7</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>92</v>
-      </c>
       <c r="F29" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G29" s="9">
         <v>49</v>
@@ -1600,22 +1601,22 @@
         <v>7</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="E30" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="F30" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1623,19 +1624,19 @@
         <v>7</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="8" t="s">
+      <c r="E31" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>99</v>
-      </c>
       <c r="F31" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G31" s="9">
         <v>51</v>
@@ -1646,19 +1647,19 @@
         <v>7</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G32">
         <v>44</v>
@@ -1669,16 +1670,16 @@
         <v>7</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>15</v>
@@ -1692,19 +1693,19 @@
         <v>7</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G34">
         <v>44</v>
@@ -1715,19 +1716,19 @@
         <v>7</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G35">
         <v>44</v>
@@ -1745,15 +1746,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6312DB92-9537-FF43-91FB-B99EEBEAEDB7}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1770,92 +1771,95 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="293" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="293" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D2" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>104</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>105</v>
       </c>
       <c r="F2" s="21"/>
       <c r="G2" s="21">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="126" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D3" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="24" t="s">
-        <v>107</v>
-      </c>
       <c r="F3" s="22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G3" s="22">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="126" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>100</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>101</v>
       </c>
       <c r="G4" s="21">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="154" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="154" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>103</v>
-      </c>
       <c r="E5" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G5" s="22">
         <v>43</v>
